--- a/phase3/output/知识图谱关系表.xlsx
+++ b/phase3/output/知识图谱关系表.xlsx
@@ -65532,7 +65532,7 @@
       </c>
       <c r="J768" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
         </is>
       </c>
       <c r="K768" s="2" t="inlineStr">
@@ -65634,7 +65634,7 @@
       </c>
       <c r="J769" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
         </is>
       </c>
       <c r="K769" s="2" t="inlineStr">
@@ -65725,7 +65725,7 @@
       </c>
       <c r="J770" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
         </is>
       </c>
       <c r="K770" s="2" t="inlineStr">
@@ -65827,7 +65827,7 @@
       </c>
       <c r="J771" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
         </is>
       </c>
       <c r="K771" s="2" t="inlineStr">
@@ -65919,7 +65919,7 @@
       </c>
       <c r="J772" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
         </is>
       </c>
       <c r="K772" s="2" t="inlineStr">
@@ -66011,7 +66011,7 @@
       </c>
       <c r="J773" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
         </is>
       </c>
       <c r="K773" s="2" t="inlineStr">
@@ -66102,7 +66102,7 @@
       </c>
       <c r="J774" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
         </is>
       </c>
       <c r="K774" s="2" t="inlineStr">
@@ -66189,12 +66189,12 @@
       </c>
       <c r="I775" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J775" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>项目六明确视图查询技术分项，单独不能据此认定完整查询工作行为；课程整体直接支撑判断主要依据项目五独立业务复杂查询任务。</t>
         </is>
       </c>
       <c r="K775" s="2" t="inlineStr">
@@ -66280,12 +66280,12 @@
       </c>
       <c r="I776" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J776" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>项目六明确视图查询技术分项，单独不能据此认定完整查询工作行为；课程整体直接支撑判断主要依据项目五独立业务复杂查询任务。</t>
         </is>
       </c>
       <c r="K776" s="2" t="inlineStr">
@@ -66371,12 +66371,12 @@
       </c>
       <c r="I777" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J777" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>项目六明确视图查询技术分项，单独不能据此认定完整查询工作行为；课程整体直接支撑判断主要依据项目五独立业务复杂查询任务。</t>
         </is>
       </c>
       <c r="K777" s="2" t="inlineStr">
@@ -69692,12 +69692,12 @@
       </c>
       <c r="I813" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J813" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K813" s="2" t="inlineStr">
@@ -69783,12 +69783,12 @@
       </c>
       <c r="I814" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J814" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K814" s="2" t="inlineStr">
@@ -69874,12 +69874,12 @@
       </c>
       <c r="I815" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J815" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K815" s="2" t="inlineStr">
@@ -69965,12 +69965,12 @@
       </c>
       <c r="I816" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J816" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K816" s="2" t="inlineStr">
@@ -70056,12 +70056,12 @@
       </c>
       <c r="I817" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J817" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K817" s="2" t="inlineStr">
@@ -70147,12 +70147,12 @@
       </c>
       <c r="I818" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J818" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K818" s="2" t="inlineStr">
@@ -70238,12 +70238,12 @@
       </c>
       <c r="I819" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J819" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K819" s="2" t="inlineStr">
@@ -70329,12 +70329,12 @@
       </c>
       <c r="I820" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J820" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K820" s="2" t="inlineStr">
@@ -70420,12 +70420,12 @@
       </c>
       <c r="I821" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J821" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K821" s="2" t="inlineStr">
@@ -70511,12 +70511,12 @@
       </c>
       <c r="I822" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J822" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K822" s="2" t="inlineStr">
@@ -70602,12 +70602,12 @@
       </c>
       <c r="I823" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J823" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K823" s="2" t="inlineStr">
@@ -70693,12 +70693,12 @@
       </c>
       <c r="I824" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J824" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="K824" s="2" t="inlineStr">
@@ -70784,12 +70784,12 @@
       </c>
       <c r="I825" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J825" s="2" t="inlineStr">
         <is>
-          <t>项目八明确数据库备份基本流程及独立备份实操，对应备份动作与产物。</t>
+          <t>修订为部分支撑：课标明确数据库备份流程及实操，支撑备份技术环节；未明确业务范围的备份对象确认和备份产物记录，不能扩大为完整业务数据备份工作。</t>
         </is>
       </c>
       <c r="K825" s="2" t="inlineStr">
@@ -70875,12 +70875,12 @@
       </c>
       <c r="I826" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J826" s="2" t="inlineStr">
         <is>
-          <t>项目八明确数据库备份基本流程及独立备份实操，对应备份动作与产物。</t>
+          <t>修订为部分支撑：课标明确数据库备份流程及实操，支撑备份技术环节；未明确业务范围的备份对象确认和备份产物记录，不能扩大为完整业务数据备份工作。</t>
         </is>
       </c>
       <c r="K826" s="2" t="inlineStr">
@@ -70966,12 +70966,12 @@
       </c>
       <c r="I827" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J827" s="2" t="inlineStr">
         <is>
-          <t>项目八明确数据库备份基本流程及独立备份实操，对应备份动作与产物。</t>
+          <t>修订为部分支撑：课标明确数据库备份流程及实操，支撑备份技术环节；未明确业务范围的备份对象确认和备份产物记录，不能扩大为完整业务数据备份工作。</t>
         </is>
       </c>
       <c r="K827" s="2" t="inlineStr">
@@ -71057,12 +71057,12 @@
       </c>
       <c r="I828" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J828" s="2" t="inlineStr">
         <is>
-          <t>项目八明确恢复流程与独立备份恢复任务，对应恢复操作。</t>
+          <t>修订为部分支撑：课标明确数据库恢复实验，未明确具体业务恢复任务的对象确认及恢复结果记录要求；实验技术环节不等同完整业务数据恢复工作行为。</t>
         </is>
       </c>
       <c r="K828" s="2" t="inlineStr">
@@ -71148,12 +71148,12 @@
       </c>
       <c r="I829" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J829" s="2" t="inlineStr">
         <is>
-          <t>项目八明确恢复流程与独立备份恢复任务，对应恢复操作。</t>
+          <t>修订为部分支撑：课标明确数据库恢复实验，未明确具体业务恢复任务的对象确认及恢复结果记录要求；实验技术环节不等同完整业务数据恢复工作行为。</t>
         </is>
       </c>
       <c r="K829" s="2" t="inlineStr">
@@ -71239,12 +71239,12 @@
       </c>
       <c r="I830" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J830" s="2" t="inlineStr">
         <is>
-          <t>项目八明确恢复流程与独立备份恢复任务，对应恢复操作。</t>
+          <t>修订为部分支撑：课标明确数据库恢复实验，未明确具体业务恢复任务的对象确认及恢复结果记录要求；实验技术环节不等同完整业务数据恢复工作行为。</t>
         </is>
       </c>
       <c r="K830" s="2" t="inlineStr">
@@ -71335,7 +71335,7 @@
       </c>
       <c r="J831" s="2" t="inlineStr">
         <is>
-          <t>目标层明确权限管理与DCL，但项目内容和独立实操未明确具体授权任务。</t>
+          <t>维持部分支撑：可见目标层提及权限与DCL，但缺少访问对象、权限配置变更及结果记录的具体实操落点，不能认定完整访问权限工作行为直接支撑。</t>
         </is>
       </c>
       <c r="K831" s="2" t="inlineStr">
@@ -71422,7 +71422,7 @@
       </c>
       <c r="J832" s="2" t="inlineStr">
         <is>
-          <t>目标层明确权限管理与DCL，但项目内容和独立实操未明确具体授权任务。</t>
+          <t>维持部分支撑：可见目标层提及权限与DCL，但缺少访问对象、权限配置变更及结果记录的具体实操落点，不能认定完整访问权限工作行为直接支撑。</t>
         </is>
       </c>
       <c r="K832" s="2" t="inlineStr">
@@ -71509,7 +71509,7 @@
       </c>
       <c r="J833" s="2" t="inlineStr">
         <is>
-          <t>思政段落提及用户权限、加密与审计，但未说明安全检查或审计记录的技术训练及考核。</t>
+          <t>维持待人工审核：思政层的用户权限、加密与审计提及不能证明安全检查、审计记录核查及问题记录训练；需教师核对完整可见课标与实施资料，未模拟专家确认。</t>
         </is>
       </c>
       <c r="K833" s="2" t="inlineStr">
@@ -71597,7 +71597,7 @@
       </c>
       <c r="J834" s="2" t="inlineStr">
         <is>
-          <t>思政段落提及用户权限、加密与审计，但未说明安全检查或审计记录的技术训练及考核。</t>
+          <t>维持待人工审核：思政层的用户权限、加密与审计提及不能证明安全检查、审计记录核查及问题记录训练；需教师核对完整可见课标与实施资料，未模拟专家确认。</t>
         </is>
       </c>
       <c r="K834" s="2" t="inlineStr">
@@ -71680,12 +71680,12 @@
       </c>
       <c r="I835" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J835" s="2" t="inlineStr">
         <is>
-          <t>索引操作及有无索引查询效果对比，与基础查询性能优化行为对应。</t>
+          <t>修订为部分支撑：课标明确索引操作与有无索引效果对比，仅能确认索引优化技术环节；未明确围绕具体查询性能问题说明完整优化操作和结果的工作产出，不能扩成全面查询性能优化。</t>
         </is>
       </c>
       <c r="K835" s="2" t="inlineStr">
@@ -71774,12 +71774,12 @@
       </c>
       <c r="I836" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J836" s="2" t="inlineStr">
         <is>
-          <t>索引操作及有无索引查询效果对比，与基础查询性能优化行为对应。</t>
+          <t>修订为部分支撑：课标明确索引操作与有无索引效果对比，仅能确认索引优化技术环节；未明确围绕具体查询性能问题说明完整优化操作和结果的工作产出，不能扩成全面查询性能优化。</t>
         </is>
       </c>
       <c r="K836" s="2" t="inlineStr">
@@ -71865,12 +71865,12 @@
       </c>
       <c r="I837" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J837" s="2" t="inlineStr">
         <is>
-          <t>索引操作及有无索引查询效果对比，与基础查询性能优化行为对应。</t>
+          <t>修订为部分支撑：课标明确索引操作与有无索引效果对比，仅能确认索引优化技术环节；未明确围绕具体查询性能问题说明完整优化操作和结果的工作产出，不能扩成全面查询性能优化。</t>
         </is>
       </c>
       <c r="K837" s="2" t="inlineStr">
@@ -71959,12 +71959,12 @@
       </c>
       <c r="I838" s="2" t="inlineStr">
         <is>
-          <t>待人工审核；直接支撑</t>
+          <t>待人工审核；部分支撑</t>
         </is>
       </c>
       <c r="J838" s="2" t="inlineStr">
         <is>
-          <t>索引操作及有无索引查询效果对比，与基础查询性能优化行为对应。</t>
+          <t>修订为部分支撑：课标明确索引操作与有无索引效果对比，仅能确认索引优化技术环节；未明确围绕具体查询性能问题说明完整优化操作和结果的工作产出，不能扩成全面查询性能优化。</t>
         </is>
       </c>
       <c r="K838" s="2" t="inlineStr">
@@ -85483,7 +85483,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>岗位全部待核验，课程匹配及图谱语义联系全部待人工审核；文本支撑不等同实际培养</t>
+          <t>历史招聘及关系证据状态保留但不再新增核验任务；当前仅课程能力图谱复核，文本支撑不等同实际培养</t>
         </is>
       </c>
     </row>
